--- a/t1_confection/A1_Outputs/A1_Outputs_B_Opt_DirContractual/A-O_AR_Projections_COMPLETED.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_B_Opt_DirContractual/A-O_AR_Projections_COMPLETED.xlsx
@@ -71261,88 +71261,88 @@
         <v>590</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -71469,88 +71469,88 @@
         <v>590</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -71677,88 +71677,88 @@
         <v>590</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -71885,88 +71885,88 @@
         <v>590</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -72093,88 +72093,88 @@
         <v>590</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="12" spans="1:34">
@@ -72301,88 +72301,88 @@
         <v>590</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="14" spans="1:34">
@@ -72925,88 +72925,88 @@
         <v>590</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -73133,88 +73133,88 @@
         <v>590</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -73341,88 +73341,88 @@
         <v>590</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -73549,88 +73549,88 @@
         <v>590</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="26" spans="1:34">
@@ -73757,88 +73757,88 @@
         <v>590</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -73965,88 +73965,88 @@
         <v>590</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -74589,88 +74589,88 @@
         <v>590</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="36" spans="1:34">
@@ -74797,88 +74797,88 @@
         <v>590</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="38" spans="1:34">
@@ -75005,88 +75005,88 @@
         <v>590</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="40" spans="1:34">
@@ -75213,88 +75213,88 @@
         <v>590</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="42" spans="1:34">
@@ -75421,88 +75421,88 @@
         <v>590</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="44" spans="1:34">
@@ -75629,88 +75629,88 @@
         <v>590</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="46" spans="1:34">
@@ -76253,88 +76253,88 @@
         <v>590</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="52" spans="1:34">
@@ -76461,88 +76461,88 @@
         <v>590</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="54" spans="1:34">
@@ -76669,88 +76669,88 @@
         <v>590</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="56" spans="1:34">
@@ -76877,88 +76877,88 @@
         <v>590</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="58" spans="1:34">
@@ -77085,88 +77085,88 @@
         <v>590</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="60" spans="1:34">
@@ -77293,88 +77293,88 @@
         <v>590</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="62" spans="1:34">
@@ -77917,88 +77917,88 @@
         <v>590</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="68" spans="1:34">
@@ -78125,88 +78125,88 @@
         <v>590</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="70" spans="1:34">
@@ -78333,88 +78333,88 @@
         <v>590</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="72" spans="1:34">
@@ -78541,88 +78541,88 @@
         <v>590</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="74" spans="1:34">
@@ -78749,88 +78749,88 @@
         <v>590</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="76" spans="1:34">
@@ -78957,88 +78957,88 @@
         <v>590</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="78" spans="1:34">
@@ -79581,88 +79581,88 @@
         <v>590</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="84" spans="1:34">
@@ -79789,88 +79789,88 @@
         <v>590</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="86" spans="1:34">
@@ -79997,88 +79997,88 @@
         <v>590</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="88" spans="1:34">
@@ -80205,88 +80205,88 @@
         <v>590</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="90" spans="1:34">
@@ -80413,88 +80413,88 @@
         <v>590</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="92" spans="1:34">
@@ -80621,88 +80621,88 @@
         <v>590</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="94" spans="1:34">
@@ -81245,88 +81245,88 @@
         <v>590</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="100" spans="1:34">
@@ -81453,88 +81453,88 @@
         <v>590</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="102" spans="1:34">
@@ -81661,88 +81661,88 @@
         <v>590</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="104" spans="1:34">
@@ -81869,88 +81869,88 @@
         <v>590</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="106" spans="1:34">
@@ -82077,88 +82077,88 @@
         <v>590</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="108" spans="1:34">
@@ -82285,88 +82285,88 @@
         <v>590</v>
       </c>
       <c r="G109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="110" spans="1:34">
@@ -82909,88 +82909,88 @@
         <v>590</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="116" spans="1:34">
@@ -83117,88 +83117,88 @@
         <v>590</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="118" spans="1:34">
@@ -83325,88 +83325,88 @@
         <v>590</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="120" spans="1:34">
@@ -83533,88 +83533,88 @@
         <v>590</v>
       </c>
       <c r="G121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="122" spans="1:34">
@@ -83741,88 +83741,88 @@
         <v>590</v>
       </c>
       <c r="G123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="124" spans="1:34">
@@ -83949,88 +83949,88 @@
         <v>590</v>
       </c>
       <c r="G125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="126" spans="1:34">
@@ -84573,88 +84573,88 @@
         <v>590</v>
       </c>
       <c r="G131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="132" spans="1:34">
@@ -84781,88 +84781,88 @@
         <v>590</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="134" spans="1:34">
@@ -84989,88 +84989,88 @@
         <v>590</v>
       </c>
       <c r="G135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="136" spans="1:34">
@@ -85197,88 +85197,88 @@
         <v>590</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="138" spans="1:34">
@@ -85405,88 +85405,88 @@
         <v>590</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="140" spans="1:34">
@@ -85613,88 +85613,88 @@
         <v>590</v>
       </c>
       <c r="G141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="142" spans="1:34">
@@ -86237,88 +86237,88 @@
         <v>590</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="148" spans="1:34">
@@ -86445,88 +86445,88 @@
         <v>590</v>
       </c>
       <c r="G149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="150" spans="1:34">
@@ -86653,88 +86653,88 @@
         <v>590</v>
       </c>
       <c r="G151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="152" spans="1:34">
@@ -86861,88 +86861,88 @@
         <v>590</v>
       </c>
       <c r="G153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="154" spans="1:34">
@@ -87069,88 +87069,88 @@
         <v>590</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="156" spans="1:34">
@@ -87277,88 +87277,88 @@
         <v>590</v>
       </c>
       <c r="G157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="158" spans="1:34">

--- a/t1_confection/A1_Outputs/A1_Outputs_B_Opt_DirContractual/A-O_AR_Projections_COMPLETED.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_B_Opt_DirContractual/A-O_AR_Projections_COMPLETED.xlsx
@@ -60227,16 +60227,16 @@
         <v>1025</v>
       </c>
       <c r="G400">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H400">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I400">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J400">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K400">
         <v>0</v>
@@ -60435,16 +60435,16 @@
         <v>590</v>
       </c>
       <c r="G402">
-        <v>0</v>
+        <v>0.9829</v>
       </c>
       <c r="H402">
-        <v>0</v>
+        <v>0.9829</v>
       </c>
       <c r="I402">
-        <v>0</v>
+        <v>0.9829</v>
       </c>
       <c r="J402">
-        <v>0</v>
+        <v>0.9829</v>
       </c>
       <c r="K402">
         <v>0</v>
@@ -60643,16 +60643,16 @@
         <v>1025</v>
       </c>
       <c r="G404">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H404">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I404">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J404">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K404">
         <v>0</v>
@@ -60851,16 +60851,16 @@
         <v>590</v>
       </c>
       <c r="G406">
-        <v>0</v>
+        <v>0.9796</v>
       </c>
       <c r="H406">
-        <v>0</v>
+        <v>0.9796</v>
       </c>
       <c r="I406">
-        <v>0</v>
+        <v>0.9796</v>
       </c>
       <c r="J406">
-        <v>0</v>
+        <v>0.9796</v>
       </c>
       <c r="K406">
         <v>0</v>
@@ -61163,16 +61163,16 @@
         <v>1025</v>
       </c>
       <c r="G409">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H409">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I409">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J409">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K409">
         <v>0</v>
@@ -61371,16 +61371,16 @@
         <v>590</v>
       </c>
       <c r="G411">
-        <v>0</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="H411">
-        <v>0</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="I411">
-        <v>0</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="J411">
-        <v>0</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="K411">
         <v>0</v>
@@ -65323,16 +65323,16 @@
         <v>1025</v>
       </c>
       <c r="G449">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H449">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I449">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J449">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K449">
         <v>0</v>
@@ -65531,16 +65531,16 @@
         <v>590</v>
       </c>
       <c r="G451">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="H451">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="I451">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="J451">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="K451">
         <v>0</v>
@@ -65739,16 +65739,16 @@
         <v>1025</v>
       </c>
       <c r="G453">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H453">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I453">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J453">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K453">
         <v>0</v>
@@ -65947,16 +65947,16 @@
         <v>590</v>
       </c>
       <c r="G455">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="H455">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="I455">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="J455">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="K455">
         <v>0</v>
@@ -69483,16 +69483,16 @@
         <v>1025</v>
       </c>
       <c r="G489">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H489">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I489">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J489">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K489">
         <v>0</v>
@@ -69691,16 +69691,16 @@
         <v>590</v>
       </c>
       <c r="G491">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="H491">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="I491">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="J491">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="K491">
         <v>0</v>
@@ -69899,16 +69899,16 @@
         <v>1025</v>
       </c>
       <c r="G493">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H493">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I493">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J493">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K493">
         <v>0</v>
@@ -70107,16 +70107,16 @@
         <v>590</v>
       </c>
       <c r="G495">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="H495">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="I495">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="J495">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="K495">
         <v>0</v>
@@ -70211,16 +70211,16 @@
         <v>1025</v>
       </c>
       <c r="G496">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H496">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I496">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J496">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K496">
         <v>0</v>
@@ -70419,16 +70419,16 @@
         <v>590</v>
       </c>
       <c r="G498">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="H498">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="I498">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="J498">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="K498">
         <v>0</v>
@@ -70731,16 +70731,16 @@
         <v>1025</v>
       </c>
       <c r="G501">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H501">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I501">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J501">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K501">
         <v>0</v>
@@ -70939,16 +70939,16 @@
         <v>590</v>
       </c>
       <c r="G503">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="H503">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="I503">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="J503">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="K503">
         <v>0</v>
